--- a/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/20261021 Lembar_Coding_Codebook_1_0_2 (Claude Sonnet 5.5 Medium).xlsx
+++ b/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/20261021 Lembar_Coding_Codebook_1_0_2 (Claude Sonnet 5.5 Medium).xlsx
@@ -1123,6 +1123,7 @@
         <color rgb="FF000000"/>
         <rFont val="Noto Sans"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ُ</t>
     </r>
@@ -1300,6 +1301,7 @@
       <color rgb="FF000000"/>
       <name val="Noto Sans"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
